--- a/basedatos_partidas/salida/descompuestos/05.04.01.170.xlsx
+++ b/basedatos_partidas/salida/descompuestos/05.04.01.170.xlsx
@@ -584,10 +584,10 @@
         <v>0.15</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>16.32</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="13">
@@ -743,10 +743,10 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="H21" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="22">
@@ -762,7 +762,7 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="5" t="n">
-        <v>22.69</v>
+        <v>22.73</v>
       </c>
     </row>
   </sheetData>
